--- a/Luban/Datas/Enemy.xlsx
+++ b/Luban/Datas/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lipenghui/LeanProject/LeiTing/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546E37FC-CB03-BD42-ACA6-CB857F876BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE1BAD7-EB80-CD44-89AA-07112F8368E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4240" yWindow="2220" windowWidth="27700" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -322,9 +322,6 @@
     <t>Assets/Prefabs/Enemies/boss_helicopter_06.prefab</t>
   </si>
   <si>
-    <t>enemy_resource</t>
-  </si>
-  <si>
     <t>资源敌机</t>
   </si>
   <si>
@@ -349,6 +346,10 @@
   </si>
   <si>
     <t>enemy_spiral_windmill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_resource</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -964,7 +965,7 @@
         <v>1.8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>32</v>
@@ -1737,13 +1738,13 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
         <v>100</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -1768,13 +1769,13 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="F28" s="1">
         <v>50</v>
@@ -1786,10 +1787,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>

--- a/Luban/Datas/Enemy.xlsx
+++ b/Luban/Datas/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lipenghui/LeanProject/LeiTing/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE1BAD7-EB80-CD44-89AA-07112F8368E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7593BBB1-860F-D543-A2C6-11BD9B2C8D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4240" yWindow="2220" windowWidth="27700" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -325,10 +325,6 @@
     <t>资源敌机</t>
   </si>
   <si>
-    <t>Assets/Prefabs/Enemies/smll_helicopter_01.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_ucav</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -350,6 +346,10 @@
   </si>
   <si>
     <t>enemy_resource</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/Enemies/small_helicopter_01.prefab</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -965,7 +965,7 @@
         <v>1.8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>32</v>
@@ -1738,13 +1738,13 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
         <v>100</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -1769,13 +1769,13 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="F28" s="1">
         <v>50</v>
@@ -1787,10 +1787,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>

--- a/Luban/Datas/Enemy.xlsx
+++ b/Luban/Datas/Enemy.xlsx
@@ -1890,12 +1890,12 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>boss_level1_enemy_08</t>
+          <t>level1_enemy_08</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>关卡1小型BOSS机</t>
+          <t>关卡1测试 enemy_08</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">

--- a/Luban/Datas/Enemy.xlsx
+++ b/Luban/Datas/Enemy.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1.2</v>
@@ -1930,6 +1930,56 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>level1_split_fighter</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>关卡1分裂导弹战斗机</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Assets/Prefabs/Enemies/enemy_02.prefab</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>enemy_bullet_01</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>level1_split_fighter_split@3+0.6</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="M33" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Sound/SFX/Enemy/SFX_Enemy_Hit_01.wav</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/Enemy.xlsx
+++ b/Luban/Datas/Enemy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="R05f0ec4eff704b8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="Re1085a7ad7604e14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -112,7 +112,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -133,6 +133,14 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="3">
     <x:cellStyle name="常规" xfId="0"/>
@@ -210,6 +218,23 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -253,9 +278,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2362,6 +2387,43 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="43">
+      <x:c r="A43"/>
+      <x:c r="B43" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>boss_level_02_mid_01</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>雷翼中继舰</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Assets/Prefabs/Enemies/enemy_09.prefab</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>level1_midboss_spinning_bullet</x:v>
+      </x:c>
+      <x:c r="J43"/>
+      <x:c r="K43" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>Assets/Art/Sound/SFX/Enemy/SFX_Enemy_Hit_01.wav</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Luban/Datas/Enemy.xlsx
+++ b/Luban/Datas/Enemy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="Re1085a7ad7604e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="1" r:id="R2f8d8c95773b4228"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -914,13 +914,11 @@
           <x:t xml:space="preserve">赤焰巡航舰</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Assets/Prefabs/Enemies/boss_02.prefab</x:t>
-        </x:is>
+      <x:c r="E10" s="2" t="str">
+        <x:v>Assets/Prefabs/Enemies/BOSS_2.prefab</x:v>
       </x:c>
       <x:c r="F10" s="2" t="n">
-        <x:v>172</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G10" s="2" t="n">
         <x:v>1.2</x:v>
